--- a/template/template_quote.xlsx
+++ b/template/template_quote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usr\Demo\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE1E5C9-EDEB-4477-BC15-220C5EBCEA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4575581E-926F-407A-B0CA-57653C4CBAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -652,7 +652,7 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,6 +850,15 @@
     </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1311,60 +1320,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Line 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeShapeType="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm flipV="1">
-          <a:off x="19050" y="752475"/>
-          <a:ext cx="7753350" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -2275,8 +2230,17 @@
     <row r="3" spans="1:10">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:10" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="9" t="s">
